--- a/Dependencies/Ping_2018/fc/PTM_heatmap_data.xlsx
+++ b/Dependencies/Ping_2018/fc/PTM_heatmap_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,26 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>fcb1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>fcb2</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>fcb3</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fcb4</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fcb5</t>
         </is>
@@ -453,96 +458,111 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2-amino-3-oxo-butanoic_acid</t>
+          <t>Methylation</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02513409505156213</v>
+        <v>0.2203743179289172</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01872569755564107</v>
+        <v>0.03808830168907683</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0282558132617916</v>
+        <v>0.04109291499441332</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02385638456491919</v>
+        <v>0.04035071373076096</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06095614360440909</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DTT adduct of cysteine</t>
+          <t>Persulfide</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004654462046585579</v>
+        <v>0.008379251632278218</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002808854633346161</v>
+        <v>0.0009289829680262641</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001487148066410084</v>
+        <v>0.002935208213886666</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02485040058845748</v>
+        <v>0.003668246702796451</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005165774881729584</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Deamidation</t>
+          <t>Acetaldehyde +26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4877876224821688</v>
+        <v>0.0192722787542399</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1329524526450516</v>
+        <v>0.01579271045644649</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3070960757136824</v>
+        <v>0.004892013689811109</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1809109162839705</v>
+        <v>0.03814976570908309</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005165774881729584</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Oxidation to nitro</t>
+          <t>Deamidation followed by a methylation</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1238086904391764</v>
+        <v>0.01005510195873386</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07396650534478223</v>
+        <v>0.01207677858434143</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05056303425794285</v>
+        <v>0.007827221903697775</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1013896344009065</v>
+        <v>0.01320568813006722</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005165774881729584</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Methylation</t>
+          <t>Half of a disulfide bridge</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02141052541429367</v>
+        <v>0.008379251632278218</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03183368584458982</v>
+        <v>0.00650288077618385</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02974296132820168</v>
+        <v>0.003913610951848888</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05168883322399156</v>
+        <v>0.008070142746152193</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01962994455057242</v>
       </c>
     </row>
     <row r="7">
@@ -552,453 +572,481 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.758500444035679</v>
+        <v>4.828962715681937</v>
       </c>
       <c r="C7" t="n">
-        <v>4.883661922511191</v>
+        <v>6.590205175178318</v>
       </c>
       <c r="D7" t="n">
-        <v>3.291802244998721</v>
+        <v>5.319575686300601</v>
       </c>
       <c r="E7" t="n">
-        <v>5.00884674260949</v>
+        <v>4.531018327294177</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.237062575097453</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Deamidation followed by a methylation</t>
+          <t>Iodoacetamide derivative</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009308924093171158</v>
+        <v>0.244674147662524</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004681424388910268</v>
+        <v>0.1681459172127538</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01041003646487059</v>
+        <v>0.1291491614110133</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005964096141229796</v>
+        <v>0.2538426718335144</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1374096118540069</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Dihydroxy</t>
+          <t>Carbamylation</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3704951789082122</v>
+        <v>0.05530306077303624</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4044750672018472</v>
+        <v>0.0520230462094708</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5323990077748101</v>
+        <v>0.0313088876147911</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5248404604282221</v>
+        <v>0.09610806361326703</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.04959143886460401</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Replacement of proton with ammonium ion</t>
+          <t>Deamidation</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08098763961058908</v>
+        <v>0.6284438724208664</v>
       </c>
       <c r="C10" t="n">
-        <v>0.09924619704489768</v>
+        <v>0.4812131774376048</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1018696425490908</v>
+        <v>0.1076243011758444</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1182879068010576</v>
+        <v>0.318403813802732</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1890673606713028</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Carbamylation</t>
+          <t>Conversion of carboxylic acid to hydroxamic acid</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02420320264224501</v>
+        <v>0.01508265293810079</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02247083706676928</v>
+        <v>0.005573897808157586</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06617808895524874</v>
+        <v>0.004892013689811109</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02584441661199578</v>
+        <v>0.01907488285454155</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.003099464929037751</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Sodium adduct</t>
+          <t>Cysteine oxidation to cysteic acid</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3174343115771365</v>
+        <v>0.004189625816139109</v>
       </c>
       <c r="C12" t="n">
-        <v>0.08801077851151304</v>
+        <v>0.004644914840131321</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03792227569345714</v>
+        <v>0.01956805475924444</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3260372557205622</v>
+        <v>0.01027109076783006</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.02686202938499383</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Acrylamide adduct</t>
+          <t>Replacement of 3 protons by iron</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02420320264224501</v>
+        <v>0.03854455750847981</v>
       </c>
       <c r="C13" t="n">
-        <v>0.005617709266692321</v>
+        <v>0.01486372748842023</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01189718453128067</v>
+        <v>0.003913610951848888</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004970080117691497</v>
+        <v>0.01320568813006722</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.01756363459788059</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Iodoacetamide derivative</t>
+          <t>Sodium adduct</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1051908422528341</v>
+        <v>0.1156336725254394</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1029913365560259</v>
+        <v>0.3139962431928773</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2074571552642067</v>
+        <v>0.1007754820101089</v>
       </c>
       <c r="E14" t="n">
-        <v>0.106359714518598</v>
+        <v>0.05135545383915032</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.4545881895922034</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Missing TMT10_Lys_mono</t>
+          <t>2-amino-3-oxo-butanoic_acid</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.004654462046585579</v>
+        <v>0.03184115620265723</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001872569755564107</v>
+        <v>0.01950864232855155</v>
       </c>
       <c r="D15" t="n">
-        <v>0.004461444199230252</v>
+        <v>0.01956805475924444</v>
       </c>
       <c r="E15" t="n">
-        <v>0.005964096141229796</v>
+        <v>0.02787867494125303</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.02376256445595609</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Di-Methylation</t>
+          <t>Amidation</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0009308924093171159</v>
+        <v>0.003351700652911287</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0009362848777820535</v>
+        <v>0.001857965936052528</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001487148066410084</v>
+        <v>0.003913610951848888</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0009940160235382993</v>
+        <v>0.005135545383915032</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.007232084834421419</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Prompt loss of side chain from oxidised Met</t>
+          <t>Dehydration</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.001861784818634232</v>
+        <v>0.09217176795506039</v>
       </c>
       <c r="C17" t="n">
-        <v>0.004681424388910268</v>
+        <v>0.09661422867473148</v>
       </c>
       <c r="D17" t="n">
-        <v>0.002230722099615126</v>
+        <v>0.03620090130460221</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0009940160235382993</v>
+        <v>0.05575734988250606</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.04029304407749076</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Missing TMT10_Nterm_mono</t>
+          <t>Loss of ammonia</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.01582517095839097</v>
+        <v>0.02262397940715119</v>
       </c>
       <c r="C18" t="n">
-        <v>0.005617709266692321</v>
+        <v>0.008360846712236379</v>
       </c>
       <c r="D18" t="n">
-        <v>0.005948592265640336</v>
+        <v>0.01369763833147111</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01391622432953619</v>
+        <v>0.01834123351398225</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.01962994455057242</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Dehydration</t>
+          <t>DTT adduct of cysteine</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.09867459538761428</v>
+        <v>0.003351700652911287</v>
       </c>
       <c r="C19" t="n">
-        <v>0.03651511023350008</v>
+        <v>0.002786948904078793</v>
       </c>
       <c r="D19" t="n">
-        <v>0.04238371989268739</v>
+        <v>0.002935208213886666</v>
       </c>
       <c r="E19" t="n">
-        <v>0.03479056082384048</v>
+        <v>0.001467298681118581</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.01962994455057242</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Half of a disulfide bridge</t>
+          <t>Quinone</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.005585354455902695</v>
+        <v>0.01424472777487297</v>
       </c>
       <c r="C20" t="n">
-        <v>0.003745139511128214</v>
+        <v>0.01486372748842023</v>
       </c>
       <c r="D20" t="n">
-        <v>0.009666462431665546</v>
+        <v>0.02054645749720666</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01789228842368939</v>
+        <v>0.03154692164404949</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.009298394787113253</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 2 protons by magnesium</t>
+          <t>Addition of Glycine</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.01954874059565943</v>
+        <v>0.07876496534341526</v>
       </c>
       <c r="C21" t="n">
-        <v>0.001872569755564107</v>
+        <v>0.06781575666591728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.004461444199230252</v>
+        <v>0.05087694237403553</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01292220830599789</v>
+        <v>0.09243981691047058</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.05372405876998767</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 3 protons by iron</t>
+          <t>Carboxyethyl</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.009308924093171158</v>
+        <v>0.006703401305822574</v>
       </c>
       <c r="C22" t="n">
-        <v>0.008426563900038483</v>
+        <v>0.0009289829680262641</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01189718453128067</v>
+        <v>0.001956805475924444</v>
       </c>
       <c r="E22" t="n">
-        <v>0.01491024035307449</v>
+        <v>0.007336493405592903</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.001033154976345917</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Addition of Glycine</t>
+          <t>Reduction</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.04375194323790445</v>
+        <v>0.01675850326455644</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04213281950019241</v>
+        <v>0.03715931872105057</v>
       </c>
       <c r="D23" t="n">
-        <v>0.07733169945332437</v>
+        <v>0.02543847118701777</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04473072105922347</v>
+        <v>0.045486259114676</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.03512726919576117</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Quinone</t>
+          <t>Replacement of 2 protons by magnesium</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.01954874059565943</v>
+        <v>0.005865476142594753</v>
       </c>
       <c r="C24" t="n">
-        <v>0.01966198243342312</v>
+        <v>0.009289829680262643</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03197368342781681</v>
+        <v>0.0009784027379622219</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01192819228245959</v>
+        <v>0.003668246702796451</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.01962994455057242</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Phosphorylation</t>
+          <t>Replacement of proton with ammonium ion</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0009308924093171159</v>
+        <v>0.216184692112778</v>
       </c>
       <c r="C25" t="n">
-        <v>0.005617709266692321</v>
+        <v>0.09568524570670522</v>
       </c>
       <c r="D25" t="n">
-        <v>0.005948592265640336</v>
+        <v>0.05674735880180887</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0009940160235382993</v>
+        <v>0.118851193170605</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1053818075872835</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Loss of ammonia</t>
+          <t>Acrylamide adduct</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.007447139274536927</v>
+        <v>0.01005510195873386</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01498055804451286</v>
+        <v>0.02229559123263034</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01264075856448571</v>
+        <v>0.005870416427773331</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01491024035307449</v>
+        <v>0.01320568813006722</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.006198929858075501</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Conversion of carboxylic acid to hydroxamic acid</t>
+          <t>Dihydroxy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.001861784818634232</v>
+        <v>0.5044309482631487</v>
       </c>
       <c r="C27" t="n">
-        <v>0.007490279022256428</v>
+        <v>0.4486987735566856</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01933292486333109</v>
+        <v>0.3903826924469266</v>
       </c>
       <c r="E27" t="n">
-        <v>0.002982048070614898</v>
+        <v>0.5825175764040764</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.5641026170848706</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Persulfide</t>
+          <t>Oxidation to nitro</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.002792677227951347</v>
+        <v>0.1323921757899958</v>
       </c>
       <c r="C28" t="n">
-        <v>0.001872569755564107</v>
+        <v>0.1319155814597295</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00371787016602521</v>
+        <v>0.06946659439531776</v>
       </c>
       <c r="E28" t="n">
-        <v>0.004970080117691497</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>Cysteine oxidation to cysteic acid</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0.01117070891180539</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.01872569755564107</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.008922888398460505</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.02584441661199578</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>Reduction</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0.02141052541429367</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.008426563900038483</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.02379436906256134</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.02485040058845748</v>
+        <v>0.05062180449859103</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.1043486526109376</v>
       </c>
     </row>
   </sheetData>

--- a/Dependencies/Ping_2018/fc/PTM_heatmap_data.xlsx
+++ b/Dependencies/Ping_2018/fc/PTM_heatmap_data.xlsx
@@ -458,595 +458,595 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Methylation</t>
+          <t>Iodoacetamide derivative</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2203743179289172</v>
+        <v>0.244674147662524</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03808830168907683</v>
+        <v>0.1681459172127538</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04109291499441332</v>
+        <v>0.1291491614110133</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04035071373076096</v>
+        <v>0.2538426718335144</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06095614360440909</v>
+        <v>0.1374096118540069</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Persulfide</t>
+          <t>Replacement of proton with ammonium ion</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008379251632278218</v>
+        <v>0.216184692112778</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009289829680262641</v>
+        <v>0.09568524570670522</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002935208213886666</v>
+        <v>0.05674735880180887</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003668246702796451</v>
+        <v>0.118851193170605</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005165774881729584</v>
+        <v>0.1053818075872835</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Acetaldehyde +26</t>
+          <t>Cysteine oxidation to cysteic acid</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0192722787542399</v>
+        <v>0.004189625816139109</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01579271045644649</v>
+        <v>0.004644914840131321</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004892013689811109</v>
+        <v>0.01956805475924444</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03814976570908309</v>
+        <v>0.01027109076783006</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005165774881729584</v>
+        <v>0.02686202938499383</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Deamidation followed by a methylation</t>
+          <t>Replacement of 3 protons by iron</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01005510195873386</v>
+        <v>0.03854455750847981</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01207677858434143</v>
+        <v>0.01486372748842023</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007827221903697775</v>
+        <v>0.003913610951848888</v>
       </c>
       <c r="E5" t="n">
         <v>0.01320568813006722</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005165774881729584</v>
+        <v>0.01756363459788059</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Half of a disulfide bridge</t>
+          <t>Persulfide</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.008379251632278218</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00650288077618385</v>
+        <v>0.0009289829680262641</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003913610951848888</v>
+        <v>0.002935208213886666</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008070142746152193</v>
+        <v>0.003668246702796451</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01962994455057242</v>
+        <v>0.005165774881729584</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Oxidation or Hydroxylation</t>
+          <t>Acetaldehyde +26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.828962715681937</v>
+        <v>0.0192722787542399</v>
       </c>
       <c r="C7" t="n">
-        <v>6.590205175178318</v>
+        <v>0.01579271045644649</v>
       </c>
       <c r="D7" t="n">
-        <v>5.319575686300601</v>
+        <v>0.004892013689811109</v>
       </c>
       <c r="E7" t="n">
-        <v>4.531018327294177</v>
+        <v>0.03814976570908309</v>
       </c>
       <c r="F7" t="n">
-        <v>5.237062575097453</v>
+        <v>0.005165774881729584</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Iodoacetamide derivative</t>
+          <t>Addition of Glycine</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.244674147662524</v>
+        <v>0.07876496534341526</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1681459172127538</v>
+        <v>0.06781575666591728</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1291491614110133</v>
+        <v>0.05087694237403553</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2538426718335144</v>
+        <v>0.09243981691047058</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1374096118540069</v>
+        <v>0.05372405876998767</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Carbamylation</t>
+          <t>DTT adduct of cysteine</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05530306077303624</v>
+        <v>0.003351700652911287</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0520230462094708</v>
+        <v>0.002786948904078793</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0313088876147911</v>
+        <v>0.002935208213886666</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09610806361326703</v>
+        <v>0.001467298681118581</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04959143886460401</v>
+        <v>0.01962994455057242</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Deamidation</t>
+          <t>Deamidation followed by a methylation</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6284438724208664</v>
+        <v>0.01005510195873386</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4812131774376048</v>
+        <v>0.01207677858434143</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1076243011758444</v>
+        <v>0.007827221903697775</v>
       </c>
       <c r="E10" t="n">
-        <v>0.318403813802732</v>
+        <v>0.01320568813006722</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1890673606713028</v>
+        <v>0.005165774881729584</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Conversion of carboxylic acid to hydroxamic acid</t>
+          <t>Half of a disulfide bridge</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01508265293810079</v>
+        <v>0.008379251632278218</v>
       </c>
       <c r="C11" t="n">
-        <v>0.005573897808157586</v>
+        <v>0.00650288077618385</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004892013689811109</v>
+        <v>0.003913610951848888</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01907488285454155</v>
+        <v>0.008070142746152193</v>
       </c>
       <c r="F11" t="n">
-        <v>0.003099464929037751</v>
+        <v>0.01962994455057242</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cysteine oxidation to cysteic acid</t>
+          <t>Oxidation to nitro</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.004189625816139109</v>
+        <v>0.1323921757899958</v>
       </c>
       <c r="C12" t="n">
-        <v>0.004644914840131321</v>
+        <v>0.1319155814597295</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01956805475924444</v>
+        <v>0.06946659439531776</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01027109076783006</v>
+        <v>0.05062180449859103</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02686202938499383</v>
+        <v>0.1043486526109376</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 3 protons by iron</t>
+          <t>Conversion of carboxylic acid to hydroxamic acid</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03854455750847981</v>
+        <v>0.01508265293810079</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01486372748842023</v>
+        <v>0.005573897808157586</v>
       </c>
       <c r="D13" t="n">
-        <v>0.003913610951848888</v>
+        <v>0.004892013689811109</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01320568813006722</v>
+        <v>0.01907488285454155</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01756363459788059</v>
+        <v>0.003099464929037751</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Sodium adduct</t>
+          <t>Deamidation</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1156336725254394</v>
+        <v>0.6284438724208664</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3139962431928773</v>
+        <v>0.4812131774376048</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1007754820101089</v>
+        <v>0.1076243011758444</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05135545383915032</v>
+        <v>0.318403813802732</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4545881895922034</v>
+        <v>0.1890673606713028</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2-amino-3-oxo-butanoic_acid</t>
+          <t>Oxidation or Hydroxylation</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03184115620265723</v>
+        <v>4.828962715681937</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01950864232855155</v>
+        <v>6.590205175178318</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01956805475924444</v>
+        <v>5.319575686300601</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02787867494125303</v>
+        <v>4.531018327294177</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02376256445595609</v>
+        <v>5.237062575097453</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Amidation</t>
+          <t>Quinone</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.003351700652911287</v>
+        <v>0.01424472777487297</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001857965936052528</v>
+        <v>0.01486372748842023</v>
       </c>
       <c r="D16" t="n">
-        <v>0.003913610951848888</v>
+        <v>0.02054645749720666</v>
       </c>
       <c r="E16" t="n">
-        <v>0.005135545383915032</v>
+        <v>0.03154692164404949</v>
       </c>
       <c r="F16" t="n">
-        <v>0.007232084834421419</v>
+        <v>0.009298394787113253</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Dehydration</t>
+          <t>Carbamylation</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.09217176795506039</v>
+        <v>0.05530306077303624</v>
       </c>
       <c r="C17" t="n">
-        <v>0.09661422867473148</v>
+        <v>0.0520230462094708</v>
       </c>
       <c r="D17" t="n">
-        <v>0.03620090130460221</v>
+        <v>0.0313088876147911</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05575734988250606</v>
+        <v>0.09610806361326703</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04029304407749076</v>
+        <v>0.04959143886460401</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Loss of ammonia</t>
+          <t>2-amino-3-oxo-butanoic_acid</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02262397940715119</v>
+        <v>0.03184115620265723</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008360846712236379</v>
+        <v>0.01950864232855155</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01369763833147111</v>
+        <v>0.01956805475924444</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01834123351398225</v>
+        <v>0.02787867494125303</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01962994455057242</v>
+        <v>0.02376256445595609</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>DTT adduct of cysteine</t>
+          <t>Sodium adduct</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.003351700652911287</v>
+        <v>0.1156336725254394</v>
       </c>
       <c r="C19" t="n">
-        <v>0.002786948904078793</v>
+        <v>0.3139962431928773</v>
       </c>
       <c r="D19" t="n">
-        <v>0.002935208213886666</v>
+        <v>0.1007754820101089</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001467298681118581</v>
+        <v>0.05135545383915032</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01962994455057242</v>
+        <v>0.4545881895922034</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Quinone</t>
+          <t>Acrylamide adduct</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.01424472777487297</v>
+        <v>0.01005510195873386</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01486372748842023</v>
+        <v>0.02229559123263034</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02054645749720666</v>
+        <v>0.005870416427773331</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03154692164404949</v>
+        <v>0.01320568813006722</v>
       </c>
       <c r="F20" t="n">
-        <v>0.009298394787113253</v>
+        <v>0.006198929858075501</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Addition of Glycine</t>
+          <t>Carboxyethyl</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.07876496534341526</v>
+        <v>0.006703401305822574</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06781575666591728</v>
+        <v>0.0009289829680262641</v>
       </c>
       <c r="D21" t="n">
-        <v>0.05087694237403553</v>
+        <v>0.001956805475924444</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09243981691047058</v>
+        <v>0.007336493405592903</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05372405876998767</v>
+        <v>0.001033154976345917</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Carboxyethyl</t>
+          <t>Methylation</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.006703401305822574</v>
+        <v>0.2203743179289172</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0009289829680262641</v>
+        <v>0.03808830168907683</v>
       </c>
       <c r="D22" t="n">
-        <v>0.001956805475924444</v>
+        <v>0.04109291499441332</v>
       </c>
       <c r="E22" t="n">
-        <v>0.007336493405592903</v>
+        <v>0.04035071373076096</v>
       </c>
       <c r="F22" t="n">
-        <v>0.001033154976345917</v>
+        <v>0.06095614360440909</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Reduction</t>
+          <t>Loss of ammonia</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.01675850326455644</v>
+        <v>0.02262397940715119</v>
       </c>
       <c r="C23" t="n">
-        <v>0.03715931872105057</v>
+        <v>0.008360846712236379</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02543847118701777</v>
+        <v>0.01369763833147111</v>
       </c>
       <c r="E23" t="n">
-        <v>0.045486259114676</v>
+        <v>0.01834123351398225</v>
       </c>
       <c r="F23" t="n">
-        <v>0.03512726919576117</v>
+        <v>0.01962994455057242</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 2 protons by magnesium</t>
+          <t>Amidation</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.005865476142594753</v>
+        <v>0.003351700652911287</v>
       </c>
       <c r="C24" t="n">
-        <v>0.009289829680262643</v>
+        <v>0.001857965936052528</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0009784027379622219</v>
+        <v>0.003913610951848888</v>
       </c>
       <c r="E24" t="n">
-        <v>0.003668246702796451</v>
+        <v>0.005135545383915032</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01962994455057242</v>
+        <v>0.007232084834421419</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Replacement of proton with ammonium ion</t>
+          <t>Dihydroxy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.216184692112778</v>
+        <v>0.5044309482631487</v>
       </c>
       <c r="C25" t="n">
-        <v>0.09568524570670522</v>
+        <v>0.4486987735566856</v>
       </c>
       <c r="D25" t="n">
-        <v>0.05674735880180887</v>
+        <v>0.3903826924469266</v>
       </c>
       <c r="E25" t="n">
-        <v>0.118851193170605</v>
+        <v>0.5825175764040764</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1053818075872835</v>
+        <v>0.5641026170848706</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Acrylamide adduct</t>
+          <t>Reduction</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01005510195873386</v>
+        <v>0.01675850326455644</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02229559123263034</v>
+        <v>0.03715931872105057</v>
       </c>
       <c r="D26" t="n">
-        <v>0.005870416427773331</v>
+        <v>0.02543847118701777</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01320568813006722</v>
+        <v>0.045486259114676</v>
       </c>
       <c r="F26" t="n">
-        <v>0.006198929858075501</v>
+        <v>0.03512726919576117</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Dihydroxy</t>
+          <t>Replacement of 2 protons by magnesium</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5044309482631487</v>
+        <v>0.005865476142594753</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4486987735566856</v>
+        <v>0.009289829680262643</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3903826924469266</v>
+        <v>0.0009784027379622219</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5825175764040764</v>
+        <v>0.003668246702796451</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5641026170848706</v>
+        <v>0.01962994455057242</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Oxidation to nitro</t>
+          <t>Dehydration</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1323921757899958</v>
+        <v>0.09217176795506039</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1319155814597295</v>
+        <v>0.09661422867473148</v>
       </c>
       <c r="D28" t="n">
-        <v>0.06946659439531776</v>
+        <v>0.03620090130460221</v>
       </c>
       <c r="E28" t="n">
-        <v>0.05062180449859103</v>
+        <v>0.05575734988250606</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1043486526109376</v>
+        <v>0.04029304407749076</v>
       </c>
     </row>
   </sheetData>

--- a/Dependencies/Ping_2018/fc/PTM_heatmap_data.xlsx
+++ b/Dependencies/Ping_2018/fc/PTM_heatmap_data.xlsx
@@ -458,309 +458,309 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Iodoacetamide derivative</t>
+          <t>Acetaldehyde +26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.244674147662524</v>
+        <v>0.01367446567025393</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1681459172127538</v>
+        <v>0.01076900174521175</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1291491614110133</v>
+        <v>0.003337703499782381</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2538426718335144</v>
+        <v>0.02773290439774532</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1374096118540069</v>
+        <v>0.003642554654711317</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Replacement of proton with ammonium ion</t>
+          <t>Carbamylation</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.216184692112778</v>
+        <v>0.03923977105377215</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09568524570670522</v>
+        <v>0.03547435869010931</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05674735880180887</v>
+        <v>0.02136130239860724</v>
       </c>
       <c r="E3" t="n">
-        <v>0.118851193170605</v>
+        <v>0.06986558607893532</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1053818075872835</v>
+        <v>0.03496852468522864</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Cysteine oxidation to cysteic acid</t>
+          <t>Reduction</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004189625816139109</v>
+        <v>0.01189083971326429</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004644914840131321</v>
+        <v>0.02533882763579236</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01956805475924444</v>
+        <v>0.01735605819886838</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01027109076783006</v>
+        <v>0.03306615524346557</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02686202938499383</v>
+        <v>0.02476937165203695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 3 protons by iron</t>
+          <t>2-amino-3-oxo-butanoic_acid</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03854455750847981</v>
+        <v>0.02259259545520215</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01486372748842023</v>
+        <v>0.01330288450879099</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003913610951848888</v>
+        <v>0.01335081399912953</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01320568813006722</v>
+        <v>0.02026635321373696</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01756363459788059</v>
+        <v>0.01675575141167206</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Persulfide</t>
+          <t>Sodium adduct</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008379251632278218</v>
+        <v>0.08204679402152361</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009289829680262641</v>
+        <v>0.2141130935224454</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002935208213886666</v>
+        <v>0.06875669209551706</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003668246702796451</v>
+        <v>0.03733275592004177</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005165774881729584</v>
+        <v>0.3205448096145959</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Acetaldehyde +26</t>
+          <t>Replacement of 3 protons by iron</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0192722787542399</v>
+        <v>0.02734893134050787</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01579271045644649</v>
+        <v>0.01013553105431694</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004892013689811109</v>
+        <v>0.002670162799825905</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03814976570908309</v>
+        <v>0.009599851522296456</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005165774881729584</v>
+        <v>0.01238468582601848</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Addition of Glycine</t>
+          <t>Replacement of proton with ammonium ion</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07876496534341526</v>
+        <v>0.1533918323011093</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06781575666591728</v>
+        <v>0.06524748116216533</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05087694237403553</v>
+        <v>0.03871736059747562</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09243981691047058</v>
+        <v>0.08639866370066811</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05372405876998767</v>
+        <v>0.07430811495611087</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>DTT adduct of cysteine</t>
+          <t>Carboxyethyl</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003351700652911287</v>
+        <v>0.004756335885305716</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002786948904078793</v>
+        <v>0.0006334706908948089</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002935208213886666</v>
+        <v>0.001335081399912952</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001467298681118581</v>
+        <v>0.005333250845720253</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01962994455057242</v>
+        <v>0.0007285109309422633</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Deamidation followed by a methylation</t>
+          <t>Deamidation</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01005510195873386</v>
+        <v>0.4459064892474109</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01207677858434143</v>
+        <v>0.328137817883511</v>
       </c>
       <c r="D10" t="n">
-        <v>0.007827221903697775</v>
+        <v>0.07342947699521239</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01320568813006722</v>
+        <v>0.231463086704259</v>
       </c>
       <c r="F10" t="n">
-        <v>0.005165774881729584</v>
+        <v>0.1333175003624342</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Half of a disulfide bridge</t>
+          <t>Cysteine oxidation to cysteic acid</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.008379251632278218</v>
+        <v>0.002972709928316072</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00650288077618385</v>
+        <v>0.003167353454474045</v>
       </c>
       <c r="D11" t="n">
-        <v>0.003913610951848888</v>
+        <v>0.01335081399912953</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008070142746152193</v>
+        <v>0.007466551184008355</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01962994455057242</v>
+        <v>0.01894128420449884</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Oxidation to nitro</t>
+          <t>Dihydroxy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1323921757899958</v>
+        <v>0.3579142753692551</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1319155814597295</v>
+        <v>0.3059663437021927</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06946659439531776</v>
+        <v>0.2663487392826341</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05062180449859103</v>
+        <v>0.4234601171501881</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1043486526109376</v>
+        <v>0.3977669682944758</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Conversion of carboxylic acid to hydroxamic acid</t>
+          <t>Persulfide</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01508265293810079</v>
+        <v>0.005945419856632145</v>
       </c>
       <c r="C13" t="n">
-        <v>0.005573897808157586</v>
+        <v>0.0006334706908948089</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004892013689811109</v>
+        <v>0.002002622099869429</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01907488285454155</v>
+        <v>0.002666625422860126</v>
       </c>
       <c r="F13" t="n">
-        <v>0.003099464929037751</v>
+        <v>0.003642554654711317</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Deamidation</t>
+          <t>Addition of Glycine</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6284438724208664</v>
+        <v>0.05588694665234217</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4812131774376048</v>
+        <v>0.04624336043532105</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1076243011758444</v>
+        <v>0.03471211639773676</v>
       </c>
       <c r="E14" t="n">
-        <v>0.318403813802732</v>
+        <v>0.0671989606560752</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1890673606713028</v>
+        <v>0.03788256840899769</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Oxidation or Hydroxylation</t>
+          <t>Conversion of carboxylic acid to hydroxamic acid</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.828962715681937</v>
+        <v>0.01070175574193786</v>
       </c>
       <c r="C15" t="n">
-        <v>6.590205175178318</v>
+        <v>0.003800824145368854</v>
       </c>
       <c r="D15" t="n">
-        <v>5.319575686300601</v>
+        <v>0.003337703499782381</v>
       </c>
       <c r="E15" t="n">
-        <v>4.531018327294177</v>
+        <v>0.01386645219887266</v>
       </c>
       <c r="F15" t="n">
-        <v>5.237062575097453</v>
+        <v>0.00218553279282679</v>
       </c>
     </row>
     <row r="16">
@@ -770,85 +770,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01424472777487297</v>
+        <v>0.01010721375627465</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01486372748842023</v>
+        <v>0.01013553105431694</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02054645749720666</v>
+        <v>0.014018354699086</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03154692164404949</v>
+        <v>0.02293297863659709</v>
       </c>
       <c r="F16" t="n">
-        <v>0.009298394787113253</v>
+        <v>0.006556598378480371</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Carbamylation</t>
+          <t>Deamidation followed by a methylation</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.05530306077303624</v>
+        <v>0.007134503827958574</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0520230462094708</v>
+        <v>0.008235118981632516</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0313088876147911</v>
+        <v>0.00534032559965181</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09610806361326703</v>
+        <v>0.009599851522296456</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04959143886460401</v>
+        <v>0.003642554654711317</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2-amino-3-oxo-butanoic_acid</t>
+          <t>Dehydration</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.03184115620265723</v>
+        <v>0.0653996184229536</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01950864232855155</v>
+        <v>0.06588095185306013</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01956805475924444</v>
+        <v>0.02469900589838962</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02787867494125303</v>
+        <v>0.04053270642747393</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02376256445595609</v>
+        <v>0.02841192630674827</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Sodium adduct</t>
+          <t>Replacement of 2 protons by magnesium</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1156336725254394</v>
+        <v>0.004161793899642502</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3139962431928773</v>
+        <v>0.006334706908948089</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1007754820101089</v>
+        <v>0.0006675406999564762</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05135545383915032</v>
+        <v>0.002666625422860126</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4545881895922034</v>
+        <v>0.013841707687903</v>
       </c>
     </row>
     <row r="20">
@@ -858,63 +858,63 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.01005510195873386</v>
+        <v>0.007134503827958574</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02229559123263034</v>
+        <v>0.01520329658147541</v>
       </c>
       <c r="D20" t="n">
-        <v>0.005870416427773331</v>
+        <v>0.004005244199738858</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01320568813006722</v>
+        <v>0.009599851522296456</v>
       </c>
       <c r="F20" t="n">
-        <v>0.006198929858075501</v>
+        <v>0.00437106558565358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Carboxyethyl</t>
+          <t>DTT adduct of cysteine</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.006703401305822574</v>
+        <v>0.002378167942652858</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0009289829680262641</v>
+        <v>0.001900412072684427</v>
       </c>
       <c r="D21" t="n">
-        <v>0.001956805475924444</v>
+        <v>0.002002622099869429</v>
       </c>
       <c r="E21" t="n">
-        <v>0.007336493405592903</v>
+        <v>0.001066650169144051</v>
       </c>
       <c r="F21" t="n">
-        <v>0.001033154976345917</v>
+        <v>0.013841707687903</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Methylation</t>
+          <t>Amidation</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2203743179289172</v>
+        <v>0.002378167942652858</v>
       </c>
       <c r="C22" t="n">
-        <v>0.03808830168907683</v>
+        <v>0.001266941381789618</v>
       </c>
       <c r="D22" t="n">
-        <v>0.04109291499441332</v>
+        <v>0.002670162799825905</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04035071373076096</v>
+        <v>0.003733275592004177</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06095614360440909</v>
+        <v>0.005099576516595844</v>
       </c>
     </row>
     <row r="23">
@@ -924,129 +924,129 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.02262397940715119</v>
+        <v>0.01605263361290679</v>
       </c>
       <c r="C23" t="n">
-        <v>0.008360846712236379</v>
+        <v>0.005701236218053281</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01369763833147111</v>
+        <v>0.009345569799390668</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01834123351398225</v>
+        <v>0.01333312711430063</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01962994455057242</v>
+        <v>0.013841707687903</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Amidation</t>
+          <t>Iodoacetamide derivative</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.003351700652911287</v>
+        <v>0.1736062598136586</v>
       </c>
       <c r="C24" t="n">
-        <v>0.001857965936052528</v>
+        <v>0.1146581950519604</v>
       </c>
       <c r="D24" t="n">
-        <v>0.003913610951848888</v>
+        <v>0.08811537239425486</v>
       </c>
       <c r="E24" t="n">
-        <v>0.005135545383915032</v>
+        <v>0.1845304792619208</v>
       </c>
       <c r="F24" t="n">
-        <v>0.007232084834421419</v>
+        <v>0.09689195381532102</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Dihydroxy</t>
+          <t>Methylation</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5044309482631487</v>
+        <v>0.1563645422294254</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4486987735566856</v>
+        <v>0.02597229832668717</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3903826924469266</v>
+        <v>0.028036709398172</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5825175764040764</v>
+        <v>0.02933287965146139</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5641026170848706</v>
+        <v>0.04298214492559353</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Reduction</t>
+          <t>Oxidation or Hydroxylation</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01675850326455644</v>
+        <v>3.426345463377105</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03715931872105057</v>
+        <v>4.493841081207774</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02543847118701777</v>
+        <v>3.629418785663362</v>
       </c>
       <c r="E26" t="n">
-        <v>0.045486259114676</v>
+        <v>3.293815722316829</v>
       </c>
       <c r="F26" t="n">
-        <v>0.03512726919576117</v>
+        <v>3.692821908946333</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 2 protons by magnesium</t>
+          <t>Oxidation to nitro</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.005865476142594753</v>
+        <v>0.0939376337347879</v>
       </c>
       <c r="C27" t="n">
-        <v>0.009289829680262643</v>
+        <v>0.08995283810706288</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0009784027379622219</v>
+        <v>0.04739538969690982</v>
       </c>
       <c r="E27" t="n">
-        <v>0.003668246702796451</v>
+        <v>0.03679943083546974</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01962994455057242</v>
+        <v>0.0735796040251686</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Dehydration</t>
+          <t>Half of a disulfide bridge</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.09217176795506039</v>
+        <v>0.005945419856632145</v>
       </c>
       <c r="C28" t="n">
-        <v>0.09661422867473148</v>
+        <v>0.004434294836263663</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03620090130460221</v>
+        <v>0.002670162799825905</v>
       </c>
       <c r="E28" t="n">
-        <v>0.05575734988250606</v>
+        <v>0.005866575930292279</v>
       </c>
       <c r="F28" t="n">
-        <v>0.04029304407749076</v>
+        <v>0.013841707687903</v>
       </c>
     </row>
   </sheetData>
